--- a/education_forms/049_university_field_assessment_form--education_forms.xlsx
+++ b/education_forms/049_university_field_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'5_to_10_students'}</t>
+          <t>5_to_10_students</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '5 to 10 students'}</t>
+          <t>5 to 10 students</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'11_to_20_students'}</t>
+          <t>11_to_20_students</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '11 to 20 students'}</t>
+          <t>11 to 20 students</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'21_to_50_students'}</t>
+          <t>21_to_50_students</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '21 to 50 students'}</t>
+          <t>21 to 50 students</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'51_to_100_students'}</t>
+          <t>51_to_100_students</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '51 to 100 students'}</t>
+          <t>51 to 100 students</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_100_students'}</t>
+          <t>more_than_100_students</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'More than 100 students'}</t>
+          <t>More than 100 students</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'students'}</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Students'}</t>
+          <t>Students</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'faculty'}</t>
+          <t>faculty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Faculty'}</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
